--- a/docs/기능명세서_학습플래너.xlsx
+++ b/docs/기능명세서_학습플래너.xlsx
@@ -1093,7 +1093,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="21.75" customHeight="1" s="44">
       <c r="A4" s="47" t="inlineStr">
         <is>
@@ -1502,7 +1501,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="21.75" customHeight="1" s="44">
       <c r="A21" s="47" t="inlineStr">
         <is>
@@ -3837,7 +3835,7 @@
       </c>
       <c r="K15" s="54" t="inlineStr">
         <is>
-          <t>충족하지 못한 조건을 입력 중 실시간으로 표시하고 모두 충족해야 가입 버튼 활성화 / 이메일·닉네임을 포함한 비밀번호와 자주 쓰이는 비밀번호 목록(상위 1만 건)은 거부 / 중복 이메일이면 '이미 가입된 이메일입니다' / 비밀번호 해싱·저장은 Supabase Auth가 처리</t>
+          <t>충족하지 못한 조건을 입력 중 실시간으로 표시하고 모두 충족해야 가입 버튼 활성화 / 이메일·닉네임을 포함한 비밀번호와 자주 쓰이는 비밀번호 목록(상위 1만 건)은 거부 / 중복 이메일이면 '이미 가입된 이메일입니다' / 비밀번호 해싱·저장은 Supabase Auth가 처리 / (10-12) 가입 후 '인증 메일을 보냈어요' 안내 화면과 인증 메일 다시 보내기 · 인증 전 로그인은 '인증이 남았다'고 안내</t>
         </is>
       </c>
       <c r="L15" s="54" t="inlineStr">
@@ -5489,7 +5487,11 @@
           <t>블록 ID, 시작·종료 시각, 순수 학습시간</t>
         </is>
       </c>
-      <c r="I42" s="54" t="n"/>
+      <c r="I42" s="54" t="inlineStr">
+        <is>
+          <t>생성형 AI (블록 공부 방법)</t>
+        </is>
+      </c>
       <c r="J42" s="56" t="inlineStr">
         <is>
           <t>Must</t>
@@ -5497,7 +5499,7 @@
       </c>
       <c r="K42" s="54" t="inlineStr">
         <is>
-          <t>30분 이상 조작이 없으면 자동 일시정지 후 확인 모달 / 오프라인이면 로컬 저장 후 재접속 시 동기화</t>
+          <t>30분 이상 조작이 없으면 자동 일시정지 후 확인 모달 / 오프라인이면 로컬 저장 후 재접속 시 동기화 / (10-12 실사용자 설문 반영) 블록마다 '이 블록 공부 방법' — AI(Claude Haiku)가 같은 단원의 1/3·2/3·3/3 을 한 번에 받아 블록마다 3단계 할 일과 시간을 보여 줌. 실패하면 단원 유형·순서별 규칙 안내</t>
         </is>
       </c>
       <c r="L42" s="54" t="n"/>
@@ -5741,7 +5743,7 @@
       </c>
       <c r="K46" s="54" t="inlineStr">
         <is>
-          <t>미입력이어도 완료 처리에는 영향 없음</t>
+          <t>미입력이어도 완료 처리에는 영향 없음 / (10-12 설문 반영) 쓰는 중인 메모는 기기에 보관해 화면을 옮겨도 남음 · 저장 시점과 보는 곳(메모 모아보기) 안내</t>
         </is>
       </c>
       <c r="L46" s="54" t="n"/>
@@ -10311,7 +10313,7 @@
       </c>
       <c r="D2" s="54" t="inlineStr">
         <is>
-          <t>로그인 5회 연속 실패 시 60초 잠금 · 실패 사유 문구 통일로 계정 존재 여부 비노출(로그인·비밀번호 재설정) · 로그인 화면에 비밀번호 조합 규칙 미노출. 단, 회원가입의 중복 이메일은 '이미 가입된 이메일입니다'로 안내 (09-30 팀 결정)</t>
+          <t>로그인 5회 연속 실패 시 60초 잠금 · 실패 사유 문구 통일로 계정 존재 여부 비노출(로그인·비밀번호 재설정) · 로그인 화면에 비밀번호 조합 규칙 미노출. 단, 회원가입의 중복 이메일은 '이미 가입된 이메일입니다'로 안내 (09-30 팀 결정) · 이메일 가입은 인증 메일 확인 후 로그인 — 인증 전 로그인은 비밀번호가 맞을 때만 '인증 필요' 안내, 재발송은 가입 여부와 상관없이 같은 문구 (10-12)</t>
         </is>
       </c>
       <c r="E2" s="54" t="inlineStr">
@@ -10726,17 +10728,17 @@
       </c>
       <c r="D11" s="54" t="inlineStr">
         <is>
-          <t>AI·캘린더·알림 중 하나가 실패해도 나머지 기능은 정상 동작 · 집계 실패 시 직전 값 유지</t>
+          <t>AI·캘린더·알림 중 하나가 실패해도 나머지 기능은 정상 동작 · 집계 실패 시 직전 값 유지 · 15분 외부 점검으로 가동률 측정 · 헬스체크를 통과한 배포만 트래픽 · 5xx·예외 기록 (10-07)</t>
         </is>
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>AI 키 없음·시간 초과·비용 한도에서도 계획 생성 · 알림 작업 하나 실패해도 워커 계속</t>
+          <t>AI 키 없음·시간 초과·비용 한도에서도 계획 생성 · 알림 작업 하나 실패해도 워커 계속 · GitHub Actions uptime.yml 가동률 · /health/ready 503 시 배포 차단 · error_logs 요약 (관리자 '운영 상태')</t>
         </is>
       </c>
       <c r="F11" s="54" t="inlineStr">
         <is>
-          <t>services/llm.py(None → 대체) · services/template.py · workers/notification_worker.py(_safe) · 야간 재조정 실패 시 기존 일정 유지</t>
+          <t>services/llm.py(None → 대체) · services/template.py · workers/notification_worker.py(_safe) · 야간 재조정 실패 시 기존 일정 유지 · .github/workflows/uptime.yml · deploy-check.yml · main.py /health/ready · utils/error_monitor.py · backend/railway.*.json · docs/operations.md</t>
         </is>
       </c>
       <c r="G11" s="54" t="inlineStr">
@@ -10857,7 +10859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="43" min="1" max="1"/>
@@ -10883,7 +10885,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="44">
       <c r="A4" s="77" t="inlineStr">
         <is>
@@ -11122,8 +11123,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="44">
       <c r="A15" s="77" t="inlineStr">
         <is>
@@ -11666,7 +11665,28 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="44"/>
+    <row r="47" ht="27.75" customHeight="1" s="44">
+      <c r="A47" s="54" t="inlineStr">
+        <is>
+          <t>블록 공부 방법 (10-12 추가)</t>
+        </is>
+      </c>
+      <c r="B47" s="54" t="inlineStr">
+        <is>
+          <t>학습 코치</t>
+        </is>
+      </c>
+      <c r="C47" s="79" t="inlineStr">
+        <is>
+          <t>같은 단원의 블록(1/3·2/3·3/3)을 한 번에 — 처음 배우기 → 넓히기 → 정리·확인, 겹치지 않게 / 계획의 다른 단원 주제는 다루지 않음 / 교재·시험 사실을 지어내지 않음 / 팁은 받지 않음</t>
+        </is>
+      </c>
+      <c r="D47" s="54" t="inlineStr">
+        <is>
+          <t>JSON(blocks[part, steps 3개{text, minutes}])</t>
+        </is>
+      </c>
+    </row>
     <row r="48" ht="15.75" customHeight="1" s="44"/>
     <row r="49" ht="24" customHeight="1" s="44">
       <c r="A49" s="77" t="inlineStr">
@@ -12084,122 +12104,122 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1" s="44">
-      <c r="A74" s="77" t="inlineStr">
+    <row r="74" ht="15.75" customHeight="1" s="44">
+      <c r="A74" s="81" t="inlineStr">
+        <is>
+          <t>블록 공부 방법 실패</t>
+        </is>
+      </c>
+      <c r="B74" s="81" t="inlineStr">
+        <is>
+          <t>키 없음 · 비용 한도 · 20초 초과 · 응답 형식 오류</t>
+        </is>
+      </c>
+      <c r="C74" s="43" t="inlineStr">
+        <is>
+          <t>단원 유형 · 순서별 규칙 안내로 대체 (frontend/lib/studyGuide.js)</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="inlineStr">
+        <is>
+          <t>'AI 추천' 표시 없이 '단원 이름과 순서로 고른 일반적인 순서'</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1" s="44">
+      <c r="A75" s="77" t="inlineStr">
         <is>
           <t>⑦ AI 품질 평가 방법</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="30" customHeight="1" s="44">
-      <c r="A75" s="80" t="inlineStr">
+    <row r="76" ht="30" customHeight="1" s="44">
+      <c r="A76" s="80" t="inlineStr">
         <is>
           <t>정답셋 20문항을 만들어 정답률을 재고, 개선 전후를 기록하세요. '무엇을 바꿨더니 몇 %가 올랐다'가 발표의 핵심 슬라이드가 됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1" s="44">
-      <c r="A76" s="48" t="inlineStr">
+    <row r="77" ht="15.75" customHeight="1" s="44">
+      <c r="A77" s="48" t="inlineStr">
         <is>
           <t>평가 항목</t>
         </is>
       </c>
-      <c r="B76" s="48" t="inlineStr">
+      <c r="B77" s="48" t="inlineStr">
         <is>
           <t>측정 방법</t>
         </is>
       </c>
-      <c r="C76" s="48" t="inlineStr">
+      <c r="C77" s="48" t="inlineStr">
         <is>
           <t>목표 수치</t>
         </is>
       </c>
-      <c r="D76" s="48" t="inlineStr">
+      <c r="D77" s="48" t="inlineStr">
         <is>
           <t>측정 주기</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="27.75" customHeight="1" s="44">
-      <c r="A77" s="54" t="inlineStr">
-        <is>
-          <t>목표 추천 적합도</t>
-        </is>
-      </c>
-      <c r="B77" s="54" t="inlineStr">
-        <is>
-          <t>관심분야 20개 케이스에 대해 팀원 2명이 카드별 적합/부적합 교차 채점</t>
-        </is>
-      </c>
-      <c r="C77" s="54" t="inlineStr">
-        <is>
-          <t>상위 3장 중 2장 이상 적합 80%</t>
-        </is>
-      </c>
-      <c r="D77" s="54" t="inlineStr">
-        <is>
-          <t>주 1회</t>
         </is>
       </c>
     </row>
     <row r="78" ht="27.75" customHeight="1" s="44">
       <c r="A78" s="54" t="inlineStr">
         <is>
-          <t>일정 실현 가능성</t>
+          <t>목표 추천 적합도</t>
         </is>
       </c>
       <c r="B78" s="54" t="inlineStr">
         <is>
-          <t>생성된 일정을 규칙 검증기로 검사(마감 초과·선행 위반·하루 상한 위반 0건)</t>
-        </is>
-      </c>
-      <c r="C78" s="79" t="inlineStr">
-        <is>
-          <t>100%(미배치 명시 포함)</t>
+          <t>관심분야 20개 케이스에 대해 팀원 2명이 카드별 적합/부적합 교차 채점</t>
+        </is>
+      </c>
+      <c r="C78" s="54" t="inlineStr">
+        <is>
+          <t>상위 3장 중 2장 이상 적합 80%</t>
         </is>
       </c>
       <c r="D78" s="54" t="inlineStr">
         <is>
-          <t>배포 전 상시</t>
+          <t>주 1회</t>
         </is>
       </c>
     </row>
     <row r="79" ht="27.75" customHeight="1" s="44">
       <c r="A79" s="54" t="inlineStr">
         <is>
-          <t>학습 분해 품질</t>
+          <t>일정 실현 가능성</t>
         </is>
       </c>
       <c r="B79" s="54" t="inlineStr">
         <is>
-          <t>표준 커리큘럼 대비 누락 단원 비율</t>
+          <t>생성된 일정을 규칙 검증기로 검사(마감 초과·선행 위반·하루 상한 위반 0건)</t>
         </is>
       </c>
       <c r="C79" s="79" t="inlineStr">
         <is>
-          <t>10% 이하</t>
+          <t>100%(미배치 명시 포함)</t>
         </is>
       </c>
       <c r="D79" s="54" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>배포 전 상시</t>
         </is>
       </c>
     </row>
     <row r="80" ht="27.75" customHeight="1" s="44">
       <c r="A80" s="54" t="inlineStr">
         <is>
-          <t>공모전 추천 정확도</t>
+          <t>학습 분해 품질</t>
         </is>
       </c>
       <c r="B80" s="54" t="inlineStr">
         <is>
-          <t>추천 5건 중 자격·마감 조건을 모두 만족하는 비율(Precision@5)</t>
+          <t>표준 커리큘럼 대비 누락 단원 비율</t>
         </is>
       </c>
       <c r="C80" s="79" t="inlineStr">
         <is>
-          <t>90% 이상</t>
+          <t>10% 이하</t>
         </is>
       </c>
       <c r="D80" s="54" t="inlineStr">
@@ -12211,17 +12231,17 @@
     <row r="81" ht="27.75" customHeight="1" s="44">
       <c r="A81" s="54" t="inlineStr">
         <is>
-          <t>추천 이유 사실성</t>
+          <t>공모전 추천 정확도</t>
         </is>
       </c>
       <c r="B81" s="54" t="inlineStr">
         <is>
-          <t>이유 문장이 공고 원문으로 검증되는 비율</t>
+          <t>추천 5건 중 자격·마감 조건을 모두 만족하는 비율(Precision@5)</t>
         </is>
       </c>
       <c r="C81" s="79" t="inlineStr">
         <is>
-          <t>95% 이상</t>
+          <t>90% 이상</t>
         </is>
       </c>
       <c r="D81" s="54" t="inlineStr">
@@ -12233,42 +12253,42 @@
     <row r="82" ht="27.75" customHeight="1" s="44">
       <c r="A82" s="54" t="inlineStr">
         <is>
+          <t>추천 이유 사실성</t>
+        </is>
+      </c>
+      <c r="B82" s="54" t="inlineStr">
+        <is>
+          <t>이유 문장이 공고 원문으로 검증되는 비율</t>
+        </is>
+      </c>
+      <c r="C82" s="79" t="inlineStr">
+        <is>
+          <t>95% 이상</t>
+        </is>
+      </c>
+      <c r="D82" s="54" t="inlineStr">
+        <is>
+          <t>주 1회</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="27.75" customHeight="1" s="44">
+      <c r="A83" s="54" t="inlineStr">
+        <is>
           <t>일정 준수율</t>
         </is>
       </c>
-      <c r="B82" s="54" t="inlineStr">
+      <c r="B83" s="54" t="inlineStr">
         <is>
           <t>배정 블록 대비 완료 블록 비율(실사용자 5명)</t>
         </is>
       </c>
-      <c r="C82" s="79" t="inlineStr">
+      <c r="C83" s="79" t="inlineStr">
         <is>
           <t>60% 이상</t>
         </is>
       </c>
-      <c r="D82" s="54" t="inlineStr">
-        <is>
-          <t>주 1회</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1" s="44">
-      <c r="A83" s="81" t="inlineStr">
-        <is>
-          <t>재조정 안정성</t>
-        </is>
-      </c>
-      <c r="B83" s="81" t="inlineStr">
-        <is>
-          <t>야간 재조정으로 위치가 바뀐 블록 비율</t>
-        </is>
-      </c>
-      <c r="C83" s="43" t="inlineStr">
-        <is>
-          <t>30% 이하</t>
-        </is>
-      </c>
-      <c r="D83" s="81" t="inlineStr">
+      <c r="D83" s="54" t="inlineStr">
         <is>
           <t>주 1회</t>
         </is>
@@ -12277,166 +12297,187 @@
     <row r="84" ht="15.75" customHeight="1" s="44">
       <c r="A84" s="81" t="inlineStr">
         <is>
+          <t>재조정 안정성</t>
+        </is>
+      </c>
+      <c r="B84" s="81" t="inlineStr">
+        <is>
+          <t>야간 재조정으로 위치가 바뀐 블록 비율</t>
+        </is>
+      </c>
+      <c r="C84" s="43" t="inlineStr">
+        <is>
+          <t>30% 이하</t>
+        </is>
+      </c>
+      <c r="D84" s="81" t="inlineStr">
+        <is>
+          <t>주 1회</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="44">
+      <c r="A85" s="81" t="inlineStr">
+        <is>
           <t>중간 목표 적정성</t>
         </is>
       </c>
-      <c r="B84" s="81" t="inlineStr">
+      <c r="B85" s="81" t="inlineStr">
         <is>
           <t>체크포인트 기준일에 해당 범위를 실제로 끝낸 비율(실사용자 5명)</t>
         </is>
       </c>
-      <c r="C84" s="43" t="inlineStr">
+      <c r="C85" s="43" t="inlineStr">
         <is>
           <t>70% 이상</t>
         </is>
       </c>
-      <c r="D84" s="81" t="inlineStr">
+      <c r="D85" s="81" t="inlineStr">
         <is>
           <t>주 1회</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="24" customHeight="1" s="44">
-      <c r="A85" s="83" t="inlineStr">
+    <row r="86" ht="24" customHeight="1" s="44">
+      <c r="A86" s="83" t="inlineStr">
         <is>
           <t>⑧ 측정 이력</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="30" customHeight="1" s="44">
-      <c r="A86" s="80" t="inlineStr">
+    <row r="87" ht="30" customHeight="1" s="44">
+      <c r="A87" s="80" t="inlineStr">
         <is>
           <t>회차별로 기록해 두면 기술적 의사결정 근거가 그대로 남습니다. 날짜는 YYYY-MM-DD 형식.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="15.75" customHeight="1" s="44">
-      <c r="A87" s="48" t="inlineStr">
+    <row r="88" ht="15.75" customHeight="1" s="44">
+      <c r="A88" s="48" t="inlineStr">
         <is>
           <t>회차</t>
         </is>
       </c>
-      <c r="B87" s="48" t="inlineStr">
+      <c r="B88" s="48" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="C87" s="48" t="inlineStr">
+      <c r="C88" s="48" t="inlineStr">
         <is>
           <t>측정 결과</t>
         </is>
       </c>
-      <c r="D87" s="48" t="inlineStr">
+      <c r="D88" s="48" t="inlineStr">
         <is>
           <t>주요 개선 조치</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="27.75" customHeight="1" s="44">
-      <c r="A88" s="79" t="inlineStr">
-        <is>
-          <t>1차</t>
-        </is>
-      </c>
-      <c r="B88" s="79" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C88" s="79" t="inlineStr">
-        <is>
-          <t>(측정 예정) 기준선 수립</t>
-        </is>
-      </c>
-      <c r="D88" s="54" t="inlineStr">
-        <is>
-          <t>정답셋 20케이스 구축 후 최초 측정</t>
         </is>
       </c>
     </row>
     <row r="89" ht="27.75" customHeight="1" s="44">
       <c r="A89" s="79" t="inlineStr">
         <is>
-          <t>2차</t>
+          <t>1차</t>
         </is>
       </c>
       <c r="B89" s="79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C89" s="79" t="inlineStr">
         <is>
-          <t>(측정 예정)</t>
+          <t>기록 없음 — 저장소에 남은 첫 정답셋 측정은 3차</t>
         </is>
       </c>
       <c r="D89" s="54" t="inlineStr">
         <is>
-          <t>Claude 관련성 임계값(0.60/0.62)을 정답셋으로 확인 예정 (09-29 임베딩 → Claude 전환)</t>
+          <t>정답셋 20케이스 구축 후 최초 측정</t>
         </is>
       </c>
     </row>
     <row r="90" ht="27.75" customHeight="1" s="44">
       <c r="A90" s="79" t="inlineStr">
         <is>
-          <t>3차</t>
+          <t>2차</t>
         </is>
       </c>
       <c r="B90" s="79" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C90" s="79" t="inlineStr">
         <is>
-          <t>(측정 예정)</t>
+          <t>기록 없음 — 이 시기에 임베딩 대신 Claude 관련성 판단으로 바꿈(09-29)</t>
         </is>
       </c>
       <c r="D90" s="54" t="inlineStr">
         <is>
-          <t>재랭킹 가중치 조정 예정</t>
+          <t>Claude 관련성 임계값(0.60/0.62)을 정답셋으로 확인 예정 (09-29 임베딩 → Claude 전환)</t>
         </is>
       </c>
     </row>
     <row r="91" ht="27.75" customHeight="1" s="44">
       <c r="A91" s="79" t="inlineStr">
         <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="B91" s="79" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C91" s="79" t="inlineStr">
+        <is>
+          <t>목표 추천 적합도 태그 40% → Claude 100% · 일정 실현 가능성 100% · 공모전 Precision@5 100% · 추천 이유 사실성 100% (backend/evals/RESULTS.md)</t>
+        </is>
+      </c>
+      <c r="D91" s="54" t="inlineStr">
+        <is>
+          <t>Claude 관련성 검색 전환 후 첫 정답셋 측정</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="27.75" customHeight="1" s="44">
+      <c r="A92" s="79" t="inlineStr">
+        <is>
           <t>4차</t>
         </is>
       </c>
-      <c r="B91" s="79" t="inlineStr">
+      <c r="B92" s="79" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="C91" s="79" t="inlineStr">
-        <is>
-          <t>(측정 예정)</t>
-        </is>
-      </c>
-      <c r="D91" s="54" t="inlineStr">
+      <c r="C92" s="79" t="inlineStr">
+        <is>
+          <t>(10-13 예정) 실사용자 5명 설문 평균 4.0~4.6 · 재조정 신뢰 4.0 — docs/user-test/리포트.md</t>
+        </is>
+      </c>
+      <c r="D92" s="54" t="inlineStr">
         <is>
           <t>실사용자 5명 테스트 결과 반영 예정</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="27.75" customHeight="1" s="44">
-      <c r="A92" s="54" t="inlineStr">
+    <row r="93" ht="27.75" customHeight="1" s="44">
+      <c r="A93" s="54" t="inlineStr">
         <is>
           <t>※ 측정 후 '(측정 예정)'을 실제 수치로 교체하세요</t>
         </is>
       </c>
-      <c r="B92" s="54" t="n"/>
-      <c r="C92" s="54" t="n"/>
-      <c r="D92" s="54" t="n"/>
-    </row>
-    <row r="93" ht="27.75" customHeight="1" s="44">
-      <c r="A93" s="54" t="n"/>
       <c r="B93" s="54" t="n"/>
       <c r="C93" s="54" t="n"/>
       <c r="D93" s="54" t="n"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1" s="44"/>
+    <row r="94" ht="27.75" customHeight="1" s="44">
+      <c r="A94" s="54" t="n"/>
+      <c r="B94" s="54" t="n"/>
+      <c r="C94" s="54" t="n"/>
+      <c r="D94" s="54" t="n"/>
+    </row>
     <row r="95" ht="15.75" customHeight="1" s="44"/>
     <row r="96" ht="15.75" customHeight="1" s="44"/>
     <row r="97" ht="15.75" customHeight="1" s="44"/>
@@ -13345,24 +13386,24 @@
     <row r="1000" ht="15.75" customHeight="1" s="44"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A75:D75"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A74:D74"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="A76:D76"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -16609,7 +16650,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="44">
       <c r="A4" s="77" t="inlineStr">
         <is>
@@ -16784,8 +16824,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="44">
       <c r="A13" s="77" t="inlineStr">
         <is>

--- a/docs/기능명세서_학습플래너.xlsx
+++ b/docs/기능명세서_학습플래너.xlsx
@@ -12448,17 +12448,17 @@
       </c>
       <c r="B92" s="79" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C92" s="79" t="inlineStr">
         <is>
-          <t>(10-13 예정) 실사용자 5명 설문 평균 4.0~4.6 · 재조정 신뢰 4.0 — docs/user-test/리포트.md</t>
+          <t>목표 추천 적합도 태그 40% → Claude 100% · 일정 실현 가능성 100% · 공모전 Precision@5 100% · 추천 이유 사실성 100% (3차와 같음)</t>
         </is>
       </c>
       <c r="D92" s="54" t="inlineStr">
         <is>
-          <t>실사용자 5명 테스트 결과 반영 예정</t>
+          <t>공모전 후보 확대 · 추천 이유 검사 강화 · 블록 공부 방법 추가 뒤 재측정 — 품질 유지 확인</t>
         </is>
       </c>
     </row>
@@ -13386,24 +13386,24 @@
     <row r="1000" ht="15.75" customHeight="1" s="44"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A75:D75"/>
     <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A87:D87"/>
     <mergeCell ref="A86:D86"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="A76:D76"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/기능명세서_학습플래너.xlsx
+++ b/docs/기능명세서_학습플래너.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성가이드" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세서" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비기능명세" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI기능명세" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시_기능명세서" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시_AI기능명세" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="작성가이드" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="기능명세서" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="비기능명세" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AI기능명세" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="예시_기능명세서" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="예시_AI기능명세" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기능명세서'!$A$2:$N$200</definedName>
@@ -3166,7 +3166,7 @@
       <c r="I4" s="54" t="n"/>
       <c r="J4" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K4" s="54" t="inlineStr">
@@ -3180,7 +3180,11 @@
           <t>비회원</t>
         </is>
       </c>
-      <c r="N4" s="54" t="n"/>
+      <c r="N4" s="54" t="inlineStr">
+        <is>
+          <t>(10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45.75" customHeight="1" s="44">
       <c r="A5" s="54" t="inlineStr">
@@ -3338,7 +3342,7 @@
       <c r="I7" s="54" t="n"/>
       <c r="J7" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K7" s="54" t="inlineStr">
@@ -3354,7 +3358,7 @@
       </c>
       <c r="N7" s="54" t="inlineStr">
         <is>
-          <t>FR-PACE-02 결과 표시</t>
+          <t>FR-PACE-02 결과 표시 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3466,7 @@
       <c r="I9" s="54" t="n"/>
       <c r="J9" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K9" s="54" t="inlineStr">
@@ -3482,7 +3486,7 @@
       </c>
       <c r="N9" s="54" t="inlineStr">
         <is>
-          <t>파이프라인 3</t>
+          <t>파이프라인 3 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3586,7 @@
       <c r="I11" s="54" t="n"/>
       <c r="J11" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K11" s="54" t="inlineStr">
@@ -3602,7 +3606,7 @@
       </c>
       <c r="N11" s="54" t="inlineStr">
         <is>
-          <t>NFR-PRIV-01</t>
+          <t>NFR-PRIV-01 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4086,7 @@
       </c>
       <c r="J19" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K19" s="54" t="inlineStr">
@@ -4102,7 +4106,7 @@
       </c>
       <c r="N19" s="54" t="inlineStr">
         <is>
-          <t>콜드스타트 대응</t>
+          <t>콜드스타트 대응 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4702,7 @@
       <c r="I29" s="54" t="n"/>
       <c r="J29" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K29" s="54" t="inlineStr">
@@ -4718,7 +4722,7 @@
       </c>
       <c r="N29" s="54" t="inlineStr">
         <is>
-          <t>NFR-SEC-04</t>
+          <t>NFR-SEC-04 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4830,7 @@
       <c r="I31" s="54" t="n"/>
       <c r="J31" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K31" s="54" t="inlineStr">
@@ -4842,7 +4846,7 @@
       </c>
       <c r="N31" s="54" t="inlineStr">
         <is>
-          <t>NFR-PRIV-01</t>
+          <t>NFR-PRIV-01 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5014,7 @@
       <c r="I34" s="54" t="n"/>
       <c r="J34" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K34" s="54" t="inlineStr">
@@ -5026,7 +5030,7 @@
       </c>
       <c r="N34" s="54" t="inlineStr">
         <is>
-          <t>파이프라인 1의 산출물</t>
+          <t>파이프라인 1의 산출물 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5074,7 @@
       <c r="I35" s="54" t="n"/>
       <c r="J35" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K35" s="54" t="inlineStr">
@@ -5086,7 +5090,7 @@
       </c>
       <c r="N35" s="54" t="inlineStr">
         <is>
-          <t>FR-PACE-03·FR-ALARM-02의 입력값</t>
+          <t>FR-PACE-03·FR-ALARM-02의 입력값 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5310,7 @@
       </c>
       <c r="J39" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K39" s="54" t="inlineStr">
@@ -5326,7 +5330,7 @@
       </c>
       <c r="N39" s="54" t="inlineStr">
         <is>
-          <t>파이프라인 1 재실행</t>
+          <t>파이프라인 1 재실행 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5802,7 @@
       </c>
       <c r="J47" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K47" s="54" t="inlineStr">
@@ -5814,7 +5818,7 @@
       </c>
       <c r="N47" s="54" t="inlineStr">
         <is>
-          <t>FR-MY-05 설정 적용</t>
+          <t>FR-MY-05 설정 적용 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6126,7 @@
       </c>
       <c r="J52" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K52" s="54" t="inlineStr">
@@ -6142,7 +6146,7 @@
       </c>
       <c r="N52" s="54" t="inlineStr">
         <is>
-          <t>파이프라인 2 진입점</t>
+          <t>파이프라인 2 진입점 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6194,7 @@
       </c>
       <c r="J53" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K53" s="54" t="inlineStr">
@@ -6206,7 +6210,7 @@
       </c>
       <c r="N53" s="54" t="inlineStr">
         <is>
-          <t>AI기능명세 ③ 참조</t>
+          <t>AI기능명세 ③ 참조 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6314,7 @@
       <c r="I55" s="54" t="n"/>
       <c r="J55" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K55" s="54" t="inlineStr">
@@ -6326,7 +6330,7 @@
       </c>
       <c r="N55" s="54" t="inlineStr">
         <is>
-          <t>FR-GOAL-09와 같은 계산 모듈 사용</t>
+          <t>FR-GOAL-09와 같은 계산 모듈 사용 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6442,7 @@
       </c>
       <c r="J57" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K57" s="54" t="inlineStr">
@@ -6454,7 +6458,7 @@
       </c>
       <c r="N57" s="54" t="inlineStr">
         <is>
-          <t>AI기능명세 ③ 참조</t>
+          <t>AI기능명세 ③ 참조 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6506,7 @@
       </c>
       <c r="J58" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K58" s="54" t="inlineStr">
@@ -6518,7 +6522,7 @@
       </c>
       <c r="N58" s="54" t="inlineStr">
         <is>
-          <t>NFR-ETHIC-01/02</t>
+          <t>NFR-ETHIC-01/02 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6698,7 @@
       </c>
       <c r="J61" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K61" s="54" t="inlineStr">
@@ -6714,7 +6718,7 @@
       </c>
       <c r="N61" s="54" t="inlineStr">
         <is>
-          <t>피드백 수집</t>
+          <t>피드백 수집 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6894,7 @@
       </c>
       <c r="J64" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K64" s="54" t="inlineStr">
@@ -6910,7 +6914,7 @@
       </c>
       <c r="N64" s="54" t="inlineStr">
         <is>
-          <t>NFR-PRIV-02</t>
+          <t>NFR-PRIV-02 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7130,7 @@
       <c r="I68" s="54" t="n"/>
       <c r="J68" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K68" s="54" t="inlineStr">
@@ -7146,7 +7150,7 @@
       </c>
       <c r="N68" s="54" t="inlineStr">
         <is>
-          <t>FR-ALARM-01~04 공통 설정</t>
+          <t>FR-ALARM-01~04 공통 설정 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7194,7 @@
       <c r="I69" s="54" t="n"/>
       <c r="J69" s="56" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="K69" s="54" t="inlineStr">
@@ -7206,7 +7210,7 @@
       </c>
       <c r="N69" s="54" t="inlineStr">
         <is>
-          <t>NFR-PRIV-02</t>
+          <t>NFR-PRIV-02 / (10-19) Must 10개 압축으로 Should — 기능은 그대로 동작</t>
         </is>
       </c>
     </row>
